--- a/iwpb-sg-dashboard/sample/IWPB_SG_Driller_sixbasis.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_SG_Driller_sixbasis.xlsx
@@ -8,6 +8,7 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19802,4 +19803,74 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A8"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/iwpb-sg-dashboard/sample/IWPB_SG_Driller_sixbasis.xlsx
+++ b/iwpb-sg-dashboard/sample/IWPB_SG_Driller_sixbasis.xlsx
@@ -8,7 +8,6 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commentary" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -19803,74 +19802,4 @@
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:A8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>NII carried the half. Deposit margin held better than the plan assumed as the pass-through on time deposits was slower than expected.</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>Net Fee Income was the softer line. Investment activity thinned after the March rally and brokerage volumes have not come back, though the recurring wealth fee base is unchanged.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>Deposits ended the half broadly flat. The migration from current accounts into time deposits continued at much the same pace as the first quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>Loans grew on mortgage completions that had been sitting in the pipeline since February.</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>Cards spend was seasonally strong in June but the balance build is behind where the plan had it.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Insurance new business held up against a soft market, helped by the bancassurance push in the second quarter.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Trading Income was flat and is not expected to move materially in the second half.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>The half closed ahead of plan on revenue, with costs the watch item into the second half.</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
 </file>